--- a/artfynd/A 8853-2024 artfynd.xlsx
+++ b/artfynd/A 8853-2024 artfynd.xlsx
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118637139</v>
+        <v>118637276</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,25 +1171,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1255,6 +1255,21 @@
           <t>Blåbärsblandskog</t>
         </is>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1270,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118637276</v>
+        <v>118637139</v>
       </c>
       <c r="B7" t="n">
-        <v>79601</v>
+        <v>78484</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,25 +1297,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1364,21 +1379,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 8853-2024 artfynd.xlsx
+++ b/artfynd/A 8853-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118378181</v>
+        <v>118376300</v>
       </c>
       <c r="B2" t="n">
-        <v>79601</v>
+        <v>78484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529542</v>
+        <v>529513</v>
       </c>
       <c r="R2" t="n">
-        <v>7168685</v>
+        <v>7168601</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -769,26 +769,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118377908</v>
+        <v>118378181</v>
       </c>
       <c r="B3" t="n">
         <v>79601</v>
@@ -849,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529510</v>
+        <v>529542</v>
       </c>
       <c r="R3" t="n">
-        <v>7168611</v>
+        <v>7168685</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -904,12 +884,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -919,7 +899,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -937,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118376300</v>
+        <v>118377908</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,25 +929,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -980,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529513</v>
+        <v>529510</v>
       </c>
       <c r="R4" t="n">
-        <v>7168601</v>
+        <v>7168611</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1031,6 +1011,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118639082</v>
+        <v>118639685</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>79594</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,25 +1060,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529496</v>
+        <v>529491</v>
       </c>
       <c r="R5" t="n">
-        <v>7168601</v>
+        <v>7168626</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1129,6 +1129,11 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på tre sälgar</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1142,6 +1147,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1159,10 +1184,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118637276</v>
+        <v>118637139</v>
       </c>
       <c r="B6" t="n">
-        <v>79601</v>
+        <v>78484</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,25 +1196,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1255,21 +1280,6 @@
           <t>Blåbärsblandskog</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1285,7 +1295,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118637139</v>
+        <v>118639082</v>
       </c>
       <c r="B7" t="n">
         <v>78484</v>
@@ -1328,10 +1338,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529481</v>
+        <v>529496</v>
       </c>
       <c r="R7" t="n">
-        <v>7168670</v>
+        <v>7168601</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1396,7 +1406,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118639469</v>
+        <v>118639078</v>
       </c>
       <c r="B8" t="n">
         <v>79594</v>
@@ -1439,10 +1449,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529527</v>
+        <v>529496</v>
       </c>
       <c r="R8" t="n">
-        <v>7168717</v>
+        <v>7168601</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1490,6 +1500,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1507,10 +1537,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118639685</v>
+        <v>118637276</v>
       </c>
       <c r="B9" t="n">
-        <v>79594</v>
+        <v>79601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1523,21 +1553,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1550,10 +1580,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529491</v>
+        <v>529481</v>
       </c>
       <c r="R9" t="n">
-        <v>7168626</v>
+        <v>7168670</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1588,11 +1618,6 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>på tre sälgar</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1618,14 +1643,9 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1643,7 +1663,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118639078</v>
+        <v>118639469</v>
       </c>
       <c r="B10" t="n">
         <v>79594</v>
@@ -1686,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529496</v>
+        <v>529527</v>
       </c>
       <c r="R10" t="n">
-        <v>7168601</v>
+        <v>7168717</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1737,26 +1757,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 8853-2024 artfynd.xlsx
+++ b/artfynd/A 8853-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118376300</v>
+        <v>118378181</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529513</v>
+        <v>529542</v>
       </c>
       <c r="R2" t="n">
-        <v>7168601</v>
+        <v>7168685</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -769,6 +769,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118378181</v>
+        <v>118376300</v>
       </c>
       <c r="B3" t="n">
-        <v>79601</v>
+        <v>78484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +818,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529542</v>
+        <v>529513</v>
       </c>
       <c r="R3" t="n">
-        <v>7168685</v>
+        <v>7168601</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,26 +900,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1048,7 +1048,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118639685</v>
+        <v>118639078</v>
       </c>
       <c r="B5" t="n">
         <v>79594</v>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529491</v>
+        <v>529496</v>
       </c>
       <c r="R5" t="n">
-        <v>7168626</v>
+        <v>7168601</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1129,11 +1129,6 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på tre sälgar</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1151,12 +1146,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1166,7 +1161,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1184,7 +1179,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118637139</v>
+        <v>118639082</v>
       </c>
       <c r="B6" t="n">
         <v>78484</v>
@@ -1227,10 +1222,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529481</v>
+        <v>529496</v>
       </c>
       <c r="R6" t="n">
-        <v>7168670</v>
+        <v>7168601</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1295,7 +1290,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118639082</v>
+        <v>118637139</v>
       </c>
       <c r="B7" t="n">
         <v>78484</v>
@@ -1338,10 +1333,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529496</v>
+        <v>529481</v>
       </c>
       <c r="R7" t="n">
-        <v>7168601</v>
+        <v>7168670</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1406,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118639078</v>
+        <v>118637276</v>
       </c>
       <c r="B8" t="n">
-        <v>79594</v>
+        <v>79601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1422,21 +1417,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1449,10 +1444,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529496</v>
+        <v>529481</v>
       </c>
       <c r="R8" t="n">
-        <v>7168601</v>
+        <v>7168670</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1504,22 +1499,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1537,10 +1527,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118637276</v>
+        <v>118639685</v>
       </c>
       <c r="B9" t="n">
-        <v>79601</v>
+        <v>79594</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1553,21 +1543,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1580,10 +1570,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529481</v>
+        <v>529491</v>
       </c>
       <c r="R9" t="n">
-        <v>7168670</v>
+        <v>7168626</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1618,6 +1608,11 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på tre sälgar</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1643,9 +1638,14 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 8853-2024 artfynd.xlsx
+++ b/artfynd/A 8853-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118378181</v>
+        <v>118376300</v>
       </c>
       <c r="B2" t="n">
-        <v>79601</v>
+        <v>78491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529542</v>
+        <v>529513</v>
       </c>
       <c r="R2" t="n">
-        <v>7168685</v>
+        <v>7168601</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -769,26 +769,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118376300</v>
+        <v>118377908</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>79608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -849,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529513</v>
+        <v>529510</v>
       </c>
       <c r="R3" t="n">
-        <v>7168601</v>
+        <v>7168611</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -900,6 +880,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118377908</v>
+        <v>118378181</v>
       </c>
       <c r="B4" t="n">
-        <v>79601</v>
+        <v>79608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529510</v>
+        <v>529542</v>
       </c>
       <c r="R4" t="n">
-        <v>7168611</v>
+        <v>7168685</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118639078</v>
+        <v>118639685</v>
       </c>
       <c r="B5" t="n">
-        <v>79594</v>
+        <v>79601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529496</v>
+        <v>529491</v>
       </c>
       <c r="R5" t="n">
-        <v>7168601</v>
+        <v>7168626</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1129,6 +1129,11 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>på tre sälgar</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1146,12 +1151,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1161,7 +1166,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1179,10 +1184,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118639082</v>
+        <v>118639078</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1191,25 +1196,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1275,6 +1280,26 @@
           <t>Blåbärsblandskog</t>
         </is>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1290,10 +1315,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118637139</v>
+        <v>118639469</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
+        <v>79601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1302,25 +1327,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1333,10 +1358,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529481</v>
+        <v>529527</v>
       </c>
       <c r="R7" t="n">
-        <v>7168670</v>
+        <v>7168717</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1404,7 +1429,7 @@
         <v>118637276</v>
       </c>
       <c r="B8" t="n">
-        <v>79601</v>
+        <v>79608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1527,10 +1552,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118639685</v>
+        <v>118639082</v>
       </c>
       <c r="B9" t="n">
-        <v>79594</v>
+        <v>78491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,25 +1564,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1570,10 +1595,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529491</v>
+        <v>529496</v>
       </c>
       <c r="R9" t="n">
-        <v>7168626</v>
+        <v>7168601</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1608,11 +1633,6 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>på tre sälgar</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1626,26 +1646,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118639469</v>
+        <v>118637139</v>
       </c>
       <c r="B10" t="n">
-        <v>79594</v>
+        <v>78491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1675,25 +1675,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529527</v>
+        <v>529481</v>
       </c>
       <c r="R10" t="n">
-        <v>7168717</v>
+        <v>7168670</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 8853-2024 artfynd.xlsx
+++ b/artfynd/A 8853-2024 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118377908</v>
+        <v>118378181</v>
       </c>
       <c r="B3" t="n">
         <v>79608</v>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529510</v>
+        <v>529542</v>
       </c>
       <c r="R3" t="n">
-        <v>7168611</v>
+        <v>7168685</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -884,12 +884,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118378181</v>
+        <v>118377908</v>
       </c>
       <c r="B4" t="n">
         <v>79608</v>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529542</v>
+        <v>529510</v>
       </c>
       <c r="R4" t="n">
-        <v>7168685</v>
+        <v>7168611</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1048,7 +1048,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118639685</v>
+        <v>118639469</v>
       </c>
       <c r="B5" t="n">
         <v>79601</v>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529491</v>
+        <v>529527</v>
       </c>
       <c r="R5" t="n">
-        <v>7168626</v>
+        <v>7168717</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1129,11 +1129,6 @@
           <t>2024-07-10</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på tre sälgar</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1147,26 +1142,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1315,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118639469</v>
+        <v>118637276</v>
       </c>
       <c r="B7" t="n">
-        <v>79601</v>
+        <v>79608</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1331,21 +1306,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1358,10 +1333,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529527</v>
+        <v>529481</v>
       </c>
       <c r="R7" t="n">
-        <v>7168717</v>
+        <v>7168670</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1409,6 +1384,21 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1426,10 +1416,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118637276</v>
+        <v>118637139</v>
       </c>
       <c r="B8" t="n">
-        <v>79608</v>
+        <v>78491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1438,25 +1428,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1522,21 +1512,6 @@
           <t>Blåbärsblandskog</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1552,10 +1527,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118639082</v>
+        <v>118639685</v>
       </c>
       <c r="B9" t="n">
-        <v>78491</v>
+        <v>79601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1564,25 +1539,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1595,10 +1570,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529496</v>
+        <v>529491</v>
       </c>
       <c r="R9" t="n">
-        <v>7168601</v>
+        <v>7168626</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1633,6 +1608,11 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på tre sälgar</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1646,6 +1626,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1663,7 +1663,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118637139</v>
+        <v>118639082</v>
       </c>
       <c r="B10" t="n">
         <v>78491</v>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529481</v>
+        <v>529496</v>
       </c>
       <c r="R10" t="n">
-        <v>7168670</v>
+        <v>7168601</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 8853-2024 artfynd.xlsx
+++ b/artfynd/A 8853-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1772,6 +1772,312 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120416931</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57689</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vaerie Plaajhkije, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>529512</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7168682</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120416904</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79652</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vaerie Plaajhkije, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>529549</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7168684</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120416869</v>
+      </c>
+      <c r="B13" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vaerie Plaajhkije, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>529492</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7168680</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8853-2024 artfynd.xlsx
+++ b/artfynd/A 8853-2024 artfynd.xlsx
@@ -1876,10 +1876,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120416904</v>
+        <v>120416869</v>
       </c>
       <c r="B12" t="n">
-        <v>79652</v>
+        <v>74654</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1888,25 +1888,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529549</v>
+        <v>529492</v>
       </c>
       <c r="R12" t="n">
-        <v>7168684</v>
+        <v>7168680</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1978,10 +1978,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120416869</v>
+        <v>120416904</v>
       </c>
       <c r="B13" t="n">
-        <v>74654</v>
+        <v>79652</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1990,25 +1990,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529492</v>
+        <v>529549</v>
       </c>
       <c r="R13" t="n">
-        <v>7168680</v>
+        <v>7168684</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 8853-2024 artfynd.xlsx
+++ b/artfynd/A 8853-2024 artfynd.xlsx
@@ -1774,10 +1774,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120416931</v>
+        <v>120416904</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>79652</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1790,21 +1790,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529512</v>
+        <v>529549</v>
       </c>
       <c r="R11" t="n">
-        <v>7168682</v>
+        <v>7168684</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120416869</v>
+        <v>120416931</v>
       </c>
       <c r="B12" t="n">
-        <v>74654</v>
+        <v>57689</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1888,25 +1888,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529492</v>
+        <v>529512</v>
       </c>
       <c r="R12" t="n">
-        <v>7168680</v>
+        <v>7168682</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1978,10 +1978,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120416904</v>
+        <v>120416869</v>
       </c>
       <c r="B13" t="n">
-        <v>79652</v>
+        <v>74654</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1990,25 +1990,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529549</v>
+        <v>529492</v>
       </c>
       <c r="R13" t="n">
-        <v>7168684</v>
+        <v>7168680</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 8853-2024 artfynd.xlsx
+++ b/artfynd/A 8853-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118378181</v>
+        <v>118376247</v>
       </c>
       <c r="B2" t="n">
-        <v>79610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529542</v>
+        <v>529549</v>
       </c>
       <c r="R2" t="n">
-        <v>7168685</v>
+        <v>7168651</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -769,26 +764,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118377908</v>
+        <v>118376300</v>
       </c>
       <c r="B3" t="n">
-        <v>79610</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -849,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529510</v>
+        <v>529513</v>
       </c>
       <c r="R3" t="n">
-        <v>7168611</v>
+        <v>7168601</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -900,26 +870,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -937,19 +887,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118376300</v>
+        <v>118637139</v>
       </c>
       <c r="B4" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -980,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529513</v>
+        <v>529481</v>
       </c>
       <c r="R4" t="n">
-        <v>7168601</v>
+        <v>7168670</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1048,37 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118639469</v>
+        <v>118639082</v>
       </c>
       <c r="B5" t="n">
-        <v>79603</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1091,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529527</v>
+        <v>529496</v>
       </c>
       <c r="R5" t="n">
-        <v>7168717</v>
+        <v>7168601</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1159,56 +1099,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118639685</v>
+        <v>120416869</v>
       </c>
       <c r="B6" t="n">
-        <v>79603</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hundsjökullen, Ås lm</t>
+          <t>Vaerie Plaajhkije, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529491</v>
+        <v>529492</v>
       </c>
       <c r="R6" t="n">
-        <v>7168626</v>
+        <v>7168680</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1232,17 +1164,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>på tre sälgar</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,81 +1178,50 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118639082</v>
+        <v>118639078</v>
       </c>
       <c r="B7" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1391,6 +1287,26 @@
           <t>Blåbärsblandskog</t>
         </is>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1406,15 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118639078</v>
+        <v>118639469</v>
       </c>
       <c r="B8" t="n">
-        <v>79603</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529496</v>
+        <v>529527</v>
       </c>
       <c r="R8" t="n">
-        <v>7168601</v>
+        <v>7168717</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1500,26 +1411,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1537,37 +1428,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118637139</v>
+        <v>118639685</v>
       </c>
       <c r="B9" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1580,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529481</v>
+        <v>529491</v>
       </c>
       <c r="R9" t="n">
-        <v>7168670</v>
+        <v>7168626</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1618,6 +1504,11 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på tre sälgar</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1631,6 +1522,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1648,15 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118637276</v>
+        <v>120416904</v>
       </c>
       <c r="B10" t="n">
-        <v>79610</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1664,40 +1570,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hundsjökullen, Ås lm</t>
+          <t>Vaerie Plaajhkije, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529481</v>
+        <v>529549</v>
       </c>
       <c r="R10" t="n">
-        <v>7168670</v>
+        <v>7168684</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1721,12 +1624,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,54 +1638,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120416931</v>
+        <v>118377908</v>
       </c>
       <c r="B11" t="n">
-        <v>57704</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,37 +1667,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vaerie Plaajhkije, Ås lm</t>
+          <t>Hundsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529512</v>
+        <v>529510</v>
       </c>
       <c r="R11" t="n">
-        <v>7168682</v>
+        <v>7168611</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1844,12 +1724,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1858,33 +1738,54 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120416904</v>
+        <v>118378181</v>
       </c>
       <c r="B12" t="n">
-        <v>79676</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,37 +1793,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vaerie Plaajhkije, Ås lm</t>
+          <t>Hundsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529549</v>
+        <v>529542</v>
       </c>
       <c r="R12" t="n">
-        <v>7168684</v>
+        <v>7168685</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1946,12 +1850,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1960,71 +1864,95 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120416869</v>
+        <v>118637276</v>
       </c>
       <c r="B13" t="n">
-        <v>74674</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vaerie Plaajhkije, Ås lm</t>
+          <t>Hundsjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529492</v>
+        <v>529481</v>
       </c>
       <c r="R13" t="n">
-        <v>7168680</v>
+        <v>7168670</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2048,12 +1976,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2062,21 +1990,258 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120416931</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vaerie Plaajhkije, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>529512</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7168682</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Elijah Ourth</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Elijah Ourth</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118640578</v>
+      </c>
+      <c r="B15" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hundsjökullen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>529532</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7168625</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Lågörtblandskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Eva Mårtensson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8853-2024 artfynd.xlsx
+++ b/artfynd/A 8853-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118376247</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118376300</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118637139</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639082</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120416869</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639078</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1425,6 +1460,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639469</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,6 +1596,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118639685</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1653,6 +1698,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120416904</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1779,6 +1829,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118377908</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1905,6 +1960,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118378181</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2026,6 +2086,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118637276</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2123,6 +2188,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120416931</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2242,8 +2312,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118640578</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>